--- a/docs/dummy/서비스제공내역_샘플.xlsx
+++ b/docs/dummy/서비스제공내역_샘플.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K110"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -486,16 +486,16 @@
         <v>2026.06.01</v>
       </c>
       <c r="D5" t="str">
-        <v>10:00</v>
+        <v>09:00</v>
       </c>
       <c r="E5" t="str">
-        <v>10:50</v>
+        <v>09:50</v>
       </c>
       <c r="F5" t="str">
         <v>2026.06.01</v>
       </c>
       <c r="G5" t="str">
-        <v>10:52</v>
+        <v>09:52</v>
       </c>
       <c r="H5" t="str">
         <v>V2026060101</v>
@@ -521,16 +521,16 @@
         <v>2026.06.01</v>
       </c>
       <c r="D6" t="str">
-        <v>15:10</v>
+        <v>09:50</v>
       </c>
       <c r="E6" t="str">
-        <v>16:00</v>
+        <v>10:40</v>
       </c>
       <c r="F6" t="str">
         <v>2026.07.02</v>
       </c>
       <c r="G6" t="str">
-        <v>16:02</v>
+        <v>10:42</v>
       </c>
       <c r="H6" t="str">
         <v>V2026060102</v>
@@ -547,28 +547,28 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>이바다</v>
+        <v>한서준</v>
       </c>
       <c r="B7" t="str">
-        <v>2020.07.21</v>
+        <v>2020.02.18</v>
       </c>
       <c r="C7" t="str">
-        <v>2026.06.02</v>
+        <v>2026.06.01</v>
       </c>
       <c r="D7" t="str">
-        <v>13:30</v>
+        <v>10:40</v>
       </c>
       <c r="E7" t="str">
-        <v>14:20</v>
+        <v>11:30</v>
       </c>
       <c r="F7" t="str">
-        <v>2026.06.02</v>
+        <v>2026.06.01</v>
       </c>
       <c r="G7" t="str">
-        <v>14:22</v>
+        <v>11:32</v>
       </c>
       <c r="H7" t="str">
-        <v>V2026060203</v>
+        <v>V2026060103</v>
       </c>
       <c r="I7">
         <v>35000</v>
@@ -582,28 +582,28 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>최도윤</v>
+        <v>임도현</v>
       </c>
       <c r="B8" t="str">
-        <v>2019.09.09</v>
+        <v>2019.12.25</v>
       </c>
       <c r="C8" t="str">
-        <v>2026.06.02</v>
+        <v>2026.06.01</v>
       </c>
       <c r="D8" t="str">
-        <v>16:00</v>
+        <v>13:30</v>
       </c>
       <c r="E8" t="str">
-        <v>16:50</v>
+        <v>14:20</v>
       </c>
       <c r="F8" t="str">
-        <v>2026.06.02</v>
+        <v>2026.06.01</v>
       </c>
       <c r="G8" t="str">
-        <v>16:52</v>
+        <v>14:22</v>
       </c>
       <c r="H8" t="str">
-        <v>V2026060204</v>
+        <v>V2026060104</v>
       </c>
       <c r="I8">
         <v>35000</v>
@@ -617,28 +617,28 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>김하늘</v>
+        <v>조하린</v>
       </c>
       <c r="B9" t="str">
-        <v>2019.03.05</v>
+        <v>2018.08.14</v>
       </c>
       <c r="C9" t="str">
-        <v>2026.06.03</v>
+        <v>2026.06.01</v>
       </c>
       <c r="D9" t="str">
-        <v>10:00</v>
+        <v>14:20</v>
       </c>
       <c r="E9" t="str">
-        <v>10:50</v>
+        <v>15:10</v>
       </c>
       <c r="F9" t="str">
-        <v>2026.06.03</v>
+        <v>2026.06.01</v>
       </c>
       <c r="G9" t="str">
-        <v>10:52</v>
+        <v>15:12</v>
       </c>
       <c r="H9" t="str">
-        <v>V2026060305</v>
+        <v>V2026060105</v>
       </c>
       <c r="I9">
         <v>35000</v>
@@ -652,28 +652,28 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>정아라</v>
+        <v>이바다</v>
       </c>
       <c r="B10" t="str">
-        <v>2021.01.15</v>
+        <v>2020.07.21</v>
       </c>
       <c r="C10" t="str">
-        <v>2026.06.03</v>
+        <v>2026.06.02</v>
       </c>
       <c r="D10" t="str">
-        <v>11:30</v>
+        <v>09:00</v>
       </c>
       <c r="E10" t="str">
-        <v>12:20</v>
+        <v>09:50</v>
       </c>
       <c r="F10" t="str">
-        <v>2026.06.03</v>
+        <v>2026.06.02</v>
       </c>
       <c r="G10" t="str">
-        <v>12:22</v>
+        <v>09:52</v>
       </c>
       <c r="H10" t="str">
-        <v>V2026060306</v>
+        <v>V2026060206</v>
       </c>
       <c r="I10">
         <v>35000</v>
@@ -687,28 +687,28 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>이바다</v>
+        <v>오지우</v>
       </c>
       <c r="B11" t="str">
-        <v>2020.07.21</v>
+        <v>2018.06.30</v>
       </c>
       <c r="C11" t="str">
-        <v>2026.06.04</v>
+        <v>2026.06.02</v>
       </c>
       <c r="D11" t="str">
-        <v>13:30</v>
+        <v>09:50</v>
       </c>
       <c r="E11" t="str">
-        <v>14:20</v>
+        <v>10:40</v>
       </c>
       <c r="F11" t="str">
-        <v>2026.06.04</v>
+        <v>2026.06.02</v>
       </c>
       <c r="G11" t="str">
-        <v>14:22</v>
+        <v>10:42</v>
       </c>
       <c r="H11" t="str">
-        <v>V2026060407</v>
+        <v>V2026060208</v>
       </c>
       <c r="I11">
         <v>35000</v>
@@ -722,13 +722,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>정아라</v>
+        <v>최도윤</v>
       </c>
       <c r="B12" t="str">
-        <v>2021.01.15</v>
+        <v>2019.09.09</v>
       </c>
       <c r="C12" t="str">
-        <v>2026.06.05</v>
+        <v>2026.06.02</v>
       </c>
       <c r="D12" t="str">
         <v>11:30</v>
@@ -737,13 +737,13 @@
         <v>12:20</v>
       </c>
       <c r="F12" t="str">
-        <v>2026.06.05</v>
+        <v>2026.06.02</v>
       </c>
       <c r="G12" t="str">
         <v>12:22</v>
       </c>
       <c r="H12" t="str">
-        <v>V2026060509</v>
+        <v>V2026060207</v>
       </c>
       <c r="I12">
         <v>35000</v>
@@ -757,28 +757,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>박가온</v>
+        <v>임도현</v>
       </c>
       <c r="B13" t="str">
-        <v>2018.11.02</v>
+        <v>2019.12.25</v>
       </c>
       <c r="C13" t="str">
-        <v>2026.06.05</v>
+        <v>2026.06.02</v>
       </c>
       <c r="D13" t="str">
-        <v>15:10</v>
+        <v>13:30</v>
       </c>
       <c r="E13" t="str">
-        <v>16:00</v>
+        <v>14:20</v>
       </c>
       <c r="F13" t="str">
-        <v>2026.06.05</v>
+        <v>2026.06.02</v>
       </c>
       <c r="G13" t="str">
-        <v>16:02</v>
+        <v>14:22</v>
       </c>
       <c r="H13" t="str">
-        <v>V2026060508</v>
+        <v>V2026060209</v>
       </c>
       <c r="I13">
         <v>35000</v>
@@ -792,28 +792,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>최도윤</v>
+        <v>배은우</v>
       </c>
       <c r="B14" t="str">
-        <v>2019.09.09</v>
+        <v>2021.04.02</v>
       </c>
       <c r="C14" t="str">
-        <v>2026.06.05</v>
+        <v>2026.06.02</v>
       </c>
       <c r="D14" t="str">
-        <v>16:00</v>
+        <v>14:20</v>
       </c>
       <c r="E14" t="str">
-        <v>16:50</v>
+        <v>15:10</v>
       </c>
       <c r="F14" t="str">
-        <v>2026.06.05</v>
+        <v>2026.06.02</v>
       </c>
       <c r="G14" t="str">
-        <v>16:52</v>
+        <v>15:12</v>
       </c>
       <c r="H14" t="str">
-        <v>V2026060510</v>
+        <v>V2026060210</v>
       </c>
       <c r="I14">
         <v>35000</v>
@@ -833,22 +833,22 @@
         <v>2019.03.05</v>
       </c>
       <c r="C15" t="str">
-        <v>2026.06.08</v>
+        <v>2026.06.03</v>
       </c>
       <c r="D15" t="str">
-        <v>10:00</v>
+        <v>09:00</v>
       </c>
       <c r="E15" t="str">
-        <v>10:50</v>
+        <v>09:50</v>
       </c>
       <c r="F15" t="str">
-        <v>2026.06.08</v>
+        <v>2026.06.03</v>
       </c>
       <c r="G15" t="str">
-        <v>10:52</v>
+        <v>09:52</v>
       </c>
       <c r="H15" t="str">
-        <v>V2026060811</v>
+        <v>V2026060311</v>
       </c>
       <c r="I15">
         <v>35000</v>
@@ -862,28 +862,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>박가온</v>
+        <v>오지우</v>
       </c>
       <c r="B16" t="str">
-        <v>2018.11.02</v>
+        <v>2018.06.30</v>
       </c>
       <c r="C16" t="str">
-        <v>2026.06.08</v>
+        <v>2026.06.03</v>
       </c>
       <c r="D16" t="str">
-        <v>15:10</v>
+        <v>09:50</v>
       </c>
       <c r="E16" t="str">
-        <v>16:00</v>
+        <v>10:40</v>
       </c>
       <c r="F16" t="str">
-        <v>2026.06.08</v>
+        <v>2026.06.03</v>
       </c>
       <c r="G16" t="str">
-        <v>16:02</v>
+        <v>10:42</v>
       </c>
       <c r="H16" t="str">
-        <v>V2026060812</v>
+        <v>V2026060313</v>
       </c>
       <c r="I16">
         <v>35000</v>
@@ -897,28 +897,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>이바다</v>
+        <v>정아라</v>
       </c>
       <c r="B17" t="str">
-        <v>2020.07.21</v>
+        <v>2021.01.15</v>
       </c>
       <c r="C17" t="str">
-        <v>2026.06.09</v>
+        <v>2026.06.03</v>
       </c>
       <c r="D17" t="str">
-        <v>13:30</v>
+        <v>10:40</v>
       </c>
       <c r="E17" t="str">
-        <v>14:20</v>
+        <v>11:30</v>
       </c>
       <c r="F17" t="str">
-        <v>2026.06.09</v>
+        <v>2026.06.03</v>
       </c>
       <c r="G17" t="str">
-        <v>14:22</v>
+        <v>11:32</v>
       </c>
       <c r="H17" t="str">
-        <v>V2026060913</v>
+        <v>V2026060312</v>
       </c>
       <c r="I17">
         <v>35000</v>
@@ -932,28 +932,28 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>최도윤</v>
+        <v>조하린</v>
       </c>
       <c r="B18" t="str">
-        <v>2019.09.09</v>
+        <v>2018.08.14</v>
       </c>
       <c r="C18" t="str">
-        <v>2026.06.09</v>
+        <v>2026.06.03</v>
       </c>
       <c r="D18" t="str">
-        <v>16:00</v>
+        <v>14:20</v>
       </c>
       <c r="E18" t="str">
-        <v>16:50</v>
+        <v>15:10</v>
       </c>
       <c r="F18" t="str">
-        <v>2026.06.09</v>
+        <v>2026.06.03</v>
       </c>
       <c r="G18" t="str">
-        <v>16:52</v>
+        <v>11:48</v>
       </c>
       <c r="H18" t="str">
-        <v>V2026060914</v>
+        <v>V2026060315</v>
       </c>
       <c r="I18">
         <v>35000</v>
@@ -967,28 +967,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>김하늘</v>
+        <v>강시우</v>
       </c>
       <c r="B19" t="str">
-        <v>2019.03.05</v>
+        <v>2020.10.08</v>
       </c>
       <c r="C19" t="str">
-        <v>2026.06.10</v>
+        <v>2026.06.03</v>
       </c>
       <c r="D19" t="str">
-        <v>10:00</v>
+        <v>11:30</v>
       </c>
       <c r="E19" t="str">
-        <v>10:50</v>
+        <v>12:20</v>
       </c>
       <c r="F19" t="str">
-        <v>2026.06.10</v>
+        <v>2026.07.04</v>
       </c>
       <c r="G19" t="str">
-        <v>10:52</v>
+        <v>12:22</v>
       </c>
       <c r="H19" t="str">
-        <v>V2026061015</v>
+        <v>V2026060314</v>
       </c>
       <c r="I19">
         <v>35000</v>
@@ -997,33 +997,33 @@
         <v>햇살아동발달센터</v>
       </c>
       <c r="K19" t="str">
-        <v>정상결제</v>
+        <v>소급결제</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>정아라</v>
+        <v>이바다</v>
       </c>
       <c r="B20" t="str">
-        <v>2021.01.15</v>
+        <v>2020.07.21</v>
       </c>
       <c r="C20" t="str">
-        <v>2026.06.10</v>
+        <v>2026.06.04</v>
       </c>
       <c r="D20" t="str">
-        <v>11:30</v>
+        <v>09:00</v>
       </c>
       <c r="E20" t="str">
-        <v>12:20</v>
+        <v>09:50</v>
       </c>
       <c r="F20" t="str">
-        <v>2026.06.10</v>
+        <v>2026.06.04</v>
       </c>
       <c r="G20" t="str">
-        <v>11:08</v>
+        <v>09:52</v>
       </c>
       <c r="H20" t="str">
-        <v>V2026061016</v>
+        <v>V2026060416</v>
       </c>
       <c r="I20">
         <v>35000</v>
@@ -1037,28 +1037,28 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>이바다</v>
+        <v>한서준</v>
       </c>
       <c r="B21" t="str">
-        <v>2020.07.21</v>
+        <v>2020.02.18</v>
       </c>
       <c r="C21" t="str">
-        <v>2026.06.11</v>
+        <v>2026.06.04</v>
       </c>
       <c r="D21" t="str">
-        <v>13:30</v>
+        <v>10:40</v>
       </c>
       <c r="E21" t="str">
-        <v>14:20</v>
+        <v>11:30</v>
       </c>
       <c r="F21" t="str">
-        <v>2026.06.11</v>
+        <v>2026.06.04</v>
       </c>
       <c r="G21" t="str">
-        <v>14:22</v>
+        <v>11:32</v>
       </c>
       <c r="H21" t="str">
-        <v>V2026061117</v>
+        <v>V2026060417</v>
       </c>
       <c r="I21">
         <v>35000</v>
@@ -1072,13 +1072,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>정아라</v>
+        <v>강시우</v>
       </c>
       <c r="B22" t="str">
-        <v>2021.01.15</v>
+        <v>2020.10.08</v>
       </c>
       <c r="C22" t="str">
-        <v>2026.06.12</v>
+        <v>2026.06.04</v>
       </c>
       <c r="D22" t="str">
         <v>11:30</v>
@@ -1087,13 +1087,13 @@
         <v>12:20</v>
       </c>
       <c r="F22" t="str">
-        <v>2026.06.12</v>
+        <v>2026.06.04</v>
       </c>
       <c r="G22" t="str">
         <v>12:22</v>
       </c>
       <c r="H22" t="str">
-        <v>V2026061219</v>
+        <v>V2026060419</v>
       </c>
       <c r="I22">
         <v>35000</v>
@@ -1107,28 +1107,28 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>박가온</v>
+        <v>윤서아</v>
       </c>
       <c r="B23" t="str">
-        <v>2018.11.02</v>
+        <v>2021.05.11</v>
       </c>
       <c r="C23" t="str">
-        <v>2026.06.12</v>
+        <v>2026.06.04</v>
       </c>
       <c r="D23" t="str">
-        <v>15:10</v>
+        <v>13:30</v>
       </c>
       <c r="E23" t="str">
-        <v>16:00</v>
+        <v>14:20</v>
       </c>
       <c r="F23" t="str">
-        <v>2026.06.12</v>
+        <v>2026.07.03</v>
       </c>
       <c r="G23" t="str">
-        <v>16:02</v>
+        <v>14:22</v>
       </c>
       <c r="H23" t="str">
-        <v>V2026061218</v>
+        <v>V2026060418</v>
       </c>
       <c r="I23">
         <v>35000</v>
@@ -1137,33 +1137,33 @@
         <v>햇살아동발달센터</v>
       </c>
       <c r="K23" t="str">
-        <v>정상결제</v>
+        <v>소급결제</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>최도윤</v>
+        <v>배은우</v>
       </c>
       <c r="B24" t="str">
-        <v>2019.09.09</v>
+        <v>2021.04.02</v>
       </c>
       <c r="C24" t="str">
-        <v>2026.06.12</v>
+        <v>2026.06.04</v>
       </c>
       <c r="D24" t="str">
-        <v>16:00</v>
+        <v>14:20</v>
       </c>
       <c r="E24" t="str">
-        <v>16:50</v>
+        <v>15:10</v>
       </c>
       <c r="F24" t="str">
-        <v>2026.06.12</v>
+        <v>2026.06.04</v>
       </c>
       <c r="G24" t="str">
-        <v>16:52</v>
+        <v>15:12</v>
       </c>
       <c r="H24" t="str">
-        <v>V2026061220</v>
+        <v>V2026060420</v>
       </c>
       <c r="I24">
         <v>35000</v>
@@ -1177,28 +1177,28 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>김하늘</v>
+        <v>박가온</v>
       </c>
       <c r="B25" t="str">
-        <v>2019.03.05</v>
+        <v>2018.11.02</v>
       </c>
       <c r="C25" t="str">
-        <v>2026.06.15</v>
+        <v>2026.06.05</v>
       </c>
       <c r="D25" t="str">
-        <v>10:00</v>
+        <v>09:50</v>
       </c>
       <c r="E25" t="str">
-        <v>10:50</v>
+        <v>10:40</v>
       </c>
       <c r="F25" t="str">
-        <v>2026.06.15</v>
+        <v>2026.06.05</v>
       </c>
       <c r="G25" t="str">
-        <v>10:52</v>
+        <v>10:42</v>
       </c>
       <c r="H25" t="str">
-        <v>V2026061521</v>
+        <v>V2026060521</v>
       </c>
       <c r="I25">
         <v>35000</v>
@@ -1212,28 +1212,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>박가온</v>
+        <v>정아라</v>
       </c>
       <c r="B26" t="str">
-        <v>2018.11.02</v>
+        <v>2021.01.15</v>
       </c>
       <c r="C26" t="str">
-        <v>2026.06.15</v>
+        <v>2026.06.05</v>
       </c>
       <c r="D26" t="str">
-        <v>15:10</v>
+        <v>10:40</v>
       </c>
       <c r="E26" t="str">
-        <v>16:00</v>
+        <v>11:30</v>
       </c>
       <c r="F26" t="str">
-        <v>2026.06.15</v>
+        <v>2026.06.05</v>
       </c>
       <c r="G26" t="str">
-        <v>16:02</v>
+        <v>11:32</v>
       </c>
       <c r="H26" t="str">
-        <v>V2026061522</v>
+        <v>V2026060522</v>
       </c>
       <c r="I26">
         <v>35000</v>
@@ -1247,28 +1247,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>이바다</v>
+        <v>최도윤</v>
       </c>
       <c r="B27" t="str">
-        <v>2020.07.21</v>
+        <v>2019.09.09</v>
       </c>
       <c r="C27" t="str">
-        <v>2026.06.16</v>
+        <v>2026.06.05</v>
       </c>
       <c r="D27" t="str">
-        <v>13:30</v>
+        <v>11:30</v>
       </c>
       <c r="E27" t="str">
-        <v>14:20</v>
+        <v>12:20</v>
       </c>
       <c r="F27" t="str">
-        <v>2026.06.16</v>
+        <v>2026.06.05</v>
       </c>
       <c r="G27" t="str">
-        <v>14:22</v>
+        <v>12:22</v>
       </c>
       <c r="H27" t="str">
-        <v>V2026061623</v>
+        <v>V2026060523</v>
       </c>
       <c r="I27">
         <v>35000</v>
@@ -1282,28 +1282,28 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>최도윤</v>
+        <v>윤서아</v>
       </c>
       <c r="B28" t="str">
-        <v>2019.09.09</v>
+        <v>2021.05.11</v>
       </c>
       <c r="C28" t="str">
-        <v>2026.06.16</v>
+        <v>2026.06.05</v>
       </c>
       <c r="D28" t="str">
-        <v>16:00</v>
+        <v>13:30</v>
       </c>
       <c r="E28" t="str">
-        <v>16:50</v>
+        <v>14:20</v>
       </c>
       <c r="F28" t="str">
-        <v>2026.06.16</v>
+        <v>2026.06.05</v>
       </c>
       <c r="G28" t="str">
-        <v>16:52</v>
+        <v>14:22</v>
       </c>
       <c r="H28" t="str">
-        <v>V2026061624</v>
+        <v>V2026060524</v>
       </c>
       <c r="I28">
         <v>35000</v>
@@ -1323,22 +1323,22 @@
         <v>2019.03.05</v>
       </c>
       <c r="C29" t="str">
-        <v>2026.06.17</v>
+        <v>2026.06.08</v>
       </c>
       <c r="D29" t="str">
-        <v>10:00</v>
+        <v>09:00</v>
       </c>
       <c r="E29" t="str">
-        <v>10:50</v>
+        <v>09:50</v>
       </c>
       <c r="F29" t="str">
-        <v>2026.06.17</v>
+        <v>2026.06.08</v>
       </c>
       <c r="G29" t="str">
-        <v>10:52</v>
+        <v>09:52</v>
       </c>
       <c r="H29" t="str">
-        <v>V2026061725</v>
+        <v>V2026060825</v>
       </c>
       <c r="I29">
         <v>35000</v>
@@ -1352,28 +1352,28 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>정아라</v>
+        <v>박가온</v>
       </c>
       <c r="B30" t="str">
-        <v>2021.01.15</v>
+        <v>2018.11.02</v>
       </c>
       <c r="C30" t="str">
-        <v>2026.06.17</v>
+        <v>2026.06.08</v>
       </c>
       <c r="D30" t="str">
-        <v>11:30</v>
+        <v>09:50</v>
       </c>
       <c r="E30" t="str">
-        <v>12:20</v>
+        <v>10:40</v>
       </c>
       <c r="F30" t="str">
-        <v>2026.06.17</v>
+        <v>2026.06.08</v>
       </c>
       <c r="G30" t="str">
-        <v>12:22</v>
+        <v>10:42</v>
       </c>
       <c r="H30" t="str">
-        <v>V2026061726</v>
+        <v>V2026060826</v>
       </c>
       <c r="I30">
         <v>35000</v>
@@ -1387,28 +1387,28 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>이바다</v>
+        <v>한서준</v>
       </c>
       <c r="B31" t="str">
-        <v>2020.07.21</v>
+        <v>2020.02.18</v>
       </c>
       <c r="C31" t="str">
-        <v>2026.06.18</v>
+        <v>2026.06.08</v>
       </c>
       <c r="D31" t="str">
-        <v>13:30</v>
+        <v>10:40</v>
       </c>
       <c r="E31" t="str">
-        <v>14:20</v>
+        <v>11:30</v>
       </c>
       <c r="F31" t="str">
-        <v>2026.06.18</v>
+        <v>2026.06.08</v>
       </c>
       <c r="G31" t="str">
-        <v>14:22</v>
+        <v>11:32</v>
       </c>
       <c r="H31" t="str">
-        <v>V2026061827</v>
+        <v>V2026060827</v>
       </c>
       <c r="I31">
         <v>35000</v>
@@ -1422,28 +1422,28 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>정아라</v>
+        <v>임도현</v>
       </c>
       <c r="B32" t="str">
-        <v>2021.01.15</v>
+        <v>2019.12.25</v>
       </c>
       <c r="C32" t="str">
-        <v>2026.06.19</v>
+        <v>2026.06.08</v>
       </c>
       <c r="D32" t="str">
-        <v>11:30</v>
+        <v>13:30</v>
       </c>
       <c r="E32" t="str">
-        <v>12:20</v>
+        <v>14:20</v>
       </c>
       <c r="F32" t="str">
-        <v>2026.06.19</v>
+        <v>2026.06.08</v>
       </c>
       <c r="G32" t="str">
-        <v>12:22</v>
+        <v>14:22</v>
       </c>
       <c r="H32" t="str">
-        <v>V2026061929</v>
+        <v>V2026060828</v>
       </c>
       <c r="I32">
         <v>35000</v>
@@ -1457,28 +1457,28 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>박가온</v>
+        <v>조하린</v>
       </c>
       <c r="B33" t="str">
-        <v>2018.11.02</v>
+        <v>2018.08.14</v>
       </c>
       <c r="C33" t="str">
-        <v>2026.06.19</v>
+        <v>2026.06.08</v>
       </c>
       <c r="D33" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E33" t="str">
         <v>15:10</v>
       </c>
-      <c r="E33" t="str">
-        <v>16:00</v>
-      </c>
       <c r="F33" t="str">
-        <v>2026.06.19</v>
+        <v>2026.06.08</v>
       </c>
       <c r="G33" t="str">
-        <v>16:02</v>
+        <v>15:12</v>
       </c>
       <c r="H33" t="str">
-        <v>V2026061928</v>
+        <v>V2026060829</v>
       </c>
       <c r="I33">
         <v>35000</v>
@@ -1492,28 +1492,28 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>최도윤</v>
+        <v>이바다</v>
       </c>
       <c r="B34" t="str">
-        <v>2019.09.09</v>
+        <v>2020.07.21</v>
       </c>
       <c r="C34" t="str">
-        <v>2026.06.19</v>
+        <v>2026.06.09</v>
       </c>
       <c r="D34" t="str">
-        <v>16:00</v>
+        <v>09:00</v>
       </c>
       <c r="E34" t="str">
-        <v>16:50</v>
+        <v>09:50</v>
       </c>
       <c r="F34" t="str">
-        <v>2026.06.19</v>
+        <v>2026.06.09</v>
       </c>
       <c r="G34" t="str">
-        <v>16:52</v>
+        <v>09:52</v>
       </c>
       <c r="H34" t="str">
-        <v>V2026061930</v>
+        <v>V2026060930</v>
       </c>
       <c r="I34">
         <v>35000</v>
@@ -1527,28 +1527,28 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>김하늘</v>
+        <v>오지우</v>
       </c>
       <c r="B35" t="str">
-        <v>2019.03.05</v>
+        <v>2018.06.30</v>
       </c>
       <c r="C35" t="str">
-        <v>2026.06.22</v>
+        <v>2026.06.09</v>
       </c>
       <c r="D35" t="str">
-        <v>10:00</v>
+        <v>09:50</v>
       </c>
       <c r="E35" t="str">
-        <v>10:50</v>
+        <v>10:40</v>
       </c>
       <c r="F35" t="str">
-        <v>2026.06.22</v>
+        <v>2026.06.09</v>
       </c>
       <c r="G35" t="str">
-        <v>10:52</v>
+        <v>10:42</v>
       </c>
       <c r="H35" t="str">
-        <v>V2026062231</v>
+        <v>V2026060932</v>
       </c>
       <c r="I35">
         <v>35000</v>
@@ -1562,28 +1562,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>박가온</v>
+        <v>최도윤</v>
       </c>
       <c r="B36" t="str">
-        <v>2018.11.02</v>
+        <v>2019.09.09</v>
       </c>
       <c r="C36" t="str">
-        <v>2026.06.22</v>
+        <v>2026.06.09</v>
       </c>
       <c r="D36" t="str">
-        <v>15:10</v>
+        <v>11:30</v>
       </c>
       <c r="E36" t="str">
-        <v>16:00</v>
+        <v>12:20</v>
       </c>
       <c r="F36" t="str">
-        <v>2026.06.22</v>
+        <v>2026.06.09</v>
       </c>
       <c r="G36" t="str">
-        <v>16:02</v>
+        <v>12:22</v>
       </c>
       <c r="H36" t="str">
-        <v>V2026062232</v>
+        <v>V2026060931</v>
       </c>
       <c r="I36">
         <v>35000</v>
@@ -1597,13 +1597,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>이바다</v>
+        <v>임도현</v>
       </c>
       <c r="B37" t="str">
-        <v>2020.07.21</v>
+        <v>2019.12.25</v>
       </c>
       <c r="C37" t="str">
-        <v>2026.06.23</v>
+        <v>2026.06.09</v>
       </c>
       <c r="D37" t="str">
         <v>13:30</v>
@@ -1612,13 +1612,13 @@
         <v>14:20</v>
       </c>
       <c r="F37" t="str">
-        <v>2026.06.23</v>
+        <v>2026.06.09</v>
       </c>
       <c r="G37" t="str">
         <v>14:22</v>
       </c>
       <c r="H37" t="str">
-        <v>V2026062333</v>
+        <v>V2026060933</v>
       </c>
       <c r="I37">
         <v>35000</v>
@@ -1632,28 +1632,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>최도윤</v>
+        <v>배은우</v>
       </c>
       <c r="B38" t="str">
-        <v>2019.09.09</v>
+        <v>2021.04.02</v>
       </c>
       <c r="C38" t="str">
-        <v>2026.06.23</v>
+        <v>2026.06.09</v>
       </c>
       <c r="D38" t="str">
-        <v>16:00</v>
+        <v>14:20</v>
       </c>
       <c r="E38" t="str">
-        <v>16:50</v>
+        <v>15:10</v>
       </c>
       <c r="F38" t="str">
-        <v>2026.06.23</v>
+        <v>2026.06.09</v>
       </c>
       <c r="G38" t="str">
-        <v>16:52</v>
+        <v>15:12</v>
       </c>
       <c r="H38" t="str">
-        <v>V2026062334</v>
+        <v>V2026060934</v>
       </c>
       <c r="I38">
         <v>35000</v>
@@ -1673,22 +1673,22 @@
         <v>2019.03.05</v>
       </c>
       <c r="C39" t="str">
-        <v>2026.06.24</v>
+        <v>2026.06.10</v>
       </c>
       <c r="D39" t="str">
-        <v>10:00</v>
+        <v>09:00</v>
       </c>
       <c r="E39" t="str">
-        <v>10:50</v>
+        <v>09:50</v>
       </c>
       <c r="F39" t="str">
-        <v>2026.06.24</v>
+        <v>2026.06.10</v>
       </c>
       <c r="G39" t="str">
-        <v>10:52</v>
+        <v>09:52</v>
       </c>
       <c r="H39" t="str">
-        <v>V2026062435</v>
+        <v>V2026061035</v>
       </c>
       <c r="I39">
         <v>35000</v>
@@ -1702,28 +1702,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>정아라</v>
+        <v>오지우</v>
       </c>
       <c r="B40" t="str">
-        <v>2021.01.15</v>
+        <v>2018.06.30</v>
       </c>
       <c r="C40" t="str">
-        <v>2026.06.24</v>
+        <v>2026.06.10</v>
       </c>
       <c r="D40" t="str">
-        <v>11:30</v>
+        <v>09:50</v>
       </c>
       <c r="E40" t="str">
-        <v>12:20</v>
+        <v>10:40</v>
       </c>
       <c r="F40" t="str">
-        <v>2026.06.24</v>
+        <v>2026.06.10</v>
       </c>
       <c r="G40" t="str">
-        <v>12:22</v>
+        <v>10:42</v>
       </c>
       <c r="H40" t="str">
-        <v>V2026062436</v>
+        <v>V2026061037</v>
       </c>
       <c r="I40">
         <v>35000</v>
@@ -1737,28 +1737,28 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>이바다</v>
+        <v>정아라</v>
       </c>
       <c r="B41" t="str">
-        <v>2020.07.21</v>
+        <v>2021.01.15</v>
       </c>
       <c r="C41" t="str">
-        <v>2026.06.25</v>
+        <v>2026.06.10</v>
       </c>
       <c r="D41" t="str">
-        <v>13:30</v>
+        <v>10:40</v>
       </c>
       <c r="E41" t="str">
-        <v>14:20</v>
+        <v>11:30</v>
       </c>
       <c r="F41" t="str">
-        <v>2026.06.25</v>
+        <v>2026.06.10</v>
       </c>
       <c r="G41" t="str">
-        <v>14:22</v>
+        <v>11:32</v>
       </c>
       <c r="H41" t="str">
-        <v>V2026062537</v>
+        <v>V2026061036</v>
       </c>
       <c r="I41">
         <v>35000</v>
@@ -1772,13 +1772,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>정아라</v>
+        <v>강시우</v>
       </c>
       <c r="B42" t="str">
-        <v>2021.01.15</v>
+        <v>2020.10.08</v>
       </c>
       <c r="C42" t="str">
-        <v>2026.06.26</v>
+        <v>2026.06.10</v>
       </c>
       <c r="D42" t="str">
         <v>11:30</v>
@@ -1787,13 +1787,13 @@
         <v>12:20</v>
       </c>
       <c r="F42" t="str">
-        <v>2026.06.26</v>
+        <v>2026.06.10</v>
       </c>
       <c r="G42" t="str">
         <v>12:22</v>
       </c>
       <c r="H42" t="str">
-        <v>V2026062639</v>
+        <v>V2026061038</v>
       </c>
       <c r="I42">
         <v>35000</v>
@@ -1807,28 +1807,28 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>박가온</v>
+        <v>조하린</v>
       </c>
       <c r="B43" t="str">
-        <v>2018.11.02</v>
+        <v>2018.08.14</v>
       </c>
       <c r="C43" t="str">
-        <v>2026.06.26</v>
+        <v>2026.06.10</v>
       </c>
       <c r="D43" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E43" t="str">
         <v>15:10</v>
       </c>
-      <c r="E43" t="str">
-        <v>16:00</v>
-      </c>
       <c r="F43" t="str">
-        <v>2026.06.26</v>
+        <v>2026.06.10</v>
       </c>
       <c r="G43" t="str">
-        <v>16:02</v>
+        <v>15:12</v>
       </c>
       <c r="H43" t="str">
-        <v>V2026062638</v>
+        <v>V2026061039</v>
       </c>
       <c r="I43">
         <v>35000</v>
@@ -1842,28 +1842,28 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>최도윤</v>
+        <v>이바다</v>
       </c>
       <c r="B44" t="str">
-        <v>2019.09.09</v>
+        <v>2020.07.21</v>
       </c>
       <c r="C44" t="str">
-        <v>2026.06.26</v>
+        <v>2026.06.11</v>
       </c>
       <c r="D44" t="str">
-        <v>16:00</v>
+        <v>09:00</v>
       </c>
       <c r="E44" t="str">
-        <v>16:50</v>
+        <v>09:50</v>
       </c>
       <c r="F44" t="str">
-        <v>2026.06.26</v>
+        <v>2026.06.11</v>
       </c>
       <c r="G44" t="str">
-        <v>16:52</v>
+        <v>09:52</v>
       </c>
       <c r="H44" t="str">
-        <v>V2026062640</v>
+        <v>V2026061140</v>
       </c>
       <c r="I44">
         <v>35000</v>
@@ -1877,28 +1877,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>김하늘</v>
+        <v>한서준</v>
       </c>
       <c r="B45" t="str">
-        <v>2019.03.05</v>
+        <v>2020.02.18</v>
       </c>
       <c r="C45" t="str">
-        <v>2026.06.29</v>
+        <v>2026.06.11</v>
       </c>
       <c r="D45" t="str">
-        <v>10:00</v>
+        <v>10:40</v>
       </c>
       <c r="E45" t="str">
-        <v>10:50</v>
+        <v>11:30</v>
       </c>
       <c r="F45" t="str">
-        <v>2026.06.29</v>
+        <v>2026.06.11</v>
       </c>
       <c r="G45" t="str">
-        <v>10:52</v>
+        <v>11:32</v>
       </c>
       <c r="H45" t="str">
-        <v>V2026062941</v>
+        <v>V2026061141</v>
       </c>
       <c r="I45">
         <v>35000</v>
@@ -1912,28 +1912,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>박가온</v>
+        <v>강시우</v>
       </c>
       <c r="B46" t="str">
-        <v>2018.11.02</v>
+        <v>2020.10.08</v>
       </c>
       <c r="C46" t="str">
-        <v>2026.06.29</v>
+        <v>2026.06.11</v>
       </c>
       <c r="D46" t="str">
-        <v>15:10</v>
+        <v>11:30</v>
       </c>
       <c r="E46" t="str">
-        <v>16:00</v>
+        <v>12:20</v>
       </c>
       <c r="F46" t="str">
-        <v>2026.06.29</v>
+        <v>2026.06.11</v>
       </c>
       <c r="G46" t="str">
-        <v>16:02</v>
+        <v>12:22</v>
       </c>
       <c r="H46" t="str">
-        <v>V2026062942</v>
+        <v>V2026061143</v>
       </c>
       <c r="I46">
         <v>35000</v>
@@ -1947,13 +1947,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>이바다</v>
+        <v>윤서아</v>
       </c>
       <c r="B47" t="str">
-        <v>2020.07.21</v>
+        <v>2021.05.11</v>
       </c>
       <c r="C47" t="str">
-        <v>2026.06.30</v>
+        <v>2026.06.11</v>
       </c>
       <c r="D47" t="str">
         <v>13:30</v>
@@ -1962,13 +1962,13 @@
         <v>14:20</v>
       </c>
       <c r="F47" t="str">
-        <v>2026.06.30</v>
+        <v>2026.06.11</v>
       </c>
       <c r="G47" t="str">
         <v>14:22</v>
       </c>
       <c r="H47" t="str">
-        <v>V2026063043</v>
+        <v>V2026061142</v>
       </c>
       <c r="I47">
         <v>35000</v>
@@ -1982,42 +1982,2212 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
+        <v>배은우</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2021.04.02</v>
+      </c>
+      <c r="C48" t="str">
+        <v>2026.06.11</v>
+      </c>
+      <c r="D48" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E48" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F48" t="str">
+        <v>2026.06.11</v>
+      </c>
+      <c r="G48" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H48" t="str">
+        <v>V2026061144</v>
+      </c>
+      <c r="I48">
+        <v>35000</v>
+      </c>
+      <c r="J48" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K48" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>박가온</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2018.11.02</v>
+      </c>
+      <c r="C49" t="str">
+        <v>2026.06.12</v>
+      </c>
+      <c r="D49" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E49" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F49" t="str">
+        <v>2026.06.12</v>
+      </c>
+      <c r="G49" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H49" t="str">
+        <v>V2026061245</v>
+      </c>
+      <c r="I49">
+        <v>35000</v>
+      </c>
+      <c r="J49" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K49" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>정아라</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2021.01.15</v>
+      </c>
+      <c r="C50" t="str">
+        <v>2026.06.12</v>
+      </c>
+      <c r="D50" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E50" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F50" t="str">
+        <v>2026.06.12</v>
+      </c>
+      <c r="G50" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H50" t="str">
+        <v>V2026061246</v>
+      </c>
+      <c r="I50">
+        <v>35000</v>
+      </c>
+      <c r="J50" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K50" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
         <v>최도윤</v>
       </c>
-      <c r="B48" t="str">
+      <c r="B51" t="str">
         <v>2019.09.09</v>
       </c>
-      <c r="C48" t="str">
+      <c r="C51" t="str">
+        <v>2026.06.12</v>
+      </c>
+      <c r="D51" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E51" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F51" t="str">
+        <v>2026.06.12</v>
+      </c>
+      <c r="G51" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H51" t="str">
+        <v>V2026061247</v>
+      </c>
+      <c r="I51">
+        <v>35000</v>
+      </c>
+      <c r="J51" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K51" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>윤서아</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2021.05.11</v>
+      </c>
+      <c r="C52" t="str">
+        <v>2026.06.12</v>
+      </c>
+      <c r="D52" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E52" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F52" t="str">
+        <v>2026.06.12</v>
+      </c>
+      <c r="G52" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H52" t="str">
+        <v>V2026061248</v>
+      </c>
+      <c r="I52">
+        <v>35000</v>
+      </c>
+      <c r="J52" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K52" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>김하늘</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2019.03.05</v>
+      </c>
+      <c r="C53" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="D53" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E53" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F53" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="G53" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H53" t="str">
+        <v>V2026061549</v>
+      </c>
+      <c r="I53">
+        <v>35000</v>
+      </c>
+      <c r="J53" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K53" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>박가온</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2018.11.02</v>
+      </c>
+      <c r="C54" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="D54" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E54" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F54" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="G54" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H54" t="str">
+        <v>V2026061550</v>
+      </c>
+      <c r="I54">
+        <v>35000</v>
+      </c>
+      <c r="J54" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K54" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>한서준</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2020.02.18</v>
+      </c>
+      <c r="C55" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="D55" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E55" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F55" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="G55" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H55" t="str">
+        <v>V2026061551</v>
+      </c>
+      <c r="I55">
+        <v>35000</v>
+      </c>
+      <c r="J55" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K55" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>임도현</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2019.12.25</v>
+      </c>
+      <c r="C56" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="D56" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E56" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F56" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="G56" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H56" t="str">
+        <v>V2026061552</v>
+      </c>
+      <c r="I56">
+        <v>35000</v>
+      </c>
+      <c r="J56" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K56" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>조하린</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2018.08.14</v>
+      </c>
+      <c r="C57" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="D57" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E57" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F57" t="str">
+        <v>2026.06.15</v>
+      </c>
+      <c r="G57" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H57" t="str">
+        <v>V2026061553</v>
+      </c>
+      <c r="I57">
+        <v>35000</v>
+      </c>
+      <c r="J57" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K57" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>이바다</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2020.07.21</v>
+      </c>
+      <c r="C58" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="D58" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E58" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F58" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="G58" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H58" t="str">
+        <v>V2026061654</v>
+      </c>
+      <c r="I58">
+        <v>35000</v>
+      </c>
+      <c r="J58" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K58" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>오지우</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2018.06.30</v>
+      </c>
+      <c r="C59" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="D59" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E59" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F59" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="G59" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H59" t="str">
+        <v>V2026061656</v>
+      </c>
+      <c r="I59">
+        <v>35000</v>
+      </c>
+      <c r="J59" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K59" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>최도윤</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2019.09.09</v>
+      </c>
+      <c r="C60" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="D60" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E60" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F60" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="G60" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H60" t="str">
+        <v>V2026061655</v>
+      </c>
+      <c r="I60">
+        <v>35000</v>
+      </c>
+      <c r="J60" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K60" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>임도현</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2019.12.25</v>
+      </c>
+      <c r="C61" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="D61" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E61" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F61" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="G61" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H61" t="str">
+        <v>V2026061657</v>
+      </c>
+      <c r="I61">
+        <v>35000</v>
+      </c>
+      <c r="J61" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K61" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>배은우</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2021.04.02</v>
+      </c>
+      <c r="C62" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="D62" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E62" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F62" t="str">
+        <v>2026.06.16</v>
+      </c>
+      <c r="G62" t="str">
+        <v>14:38</v>
+      </c>
+      <c r="H62" t="str">
+        <v>V2026061658</v>
+      </c>
+      <c r="I62">
+        <v>35000</v>
+      </c>
+      <c r="J62" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K62" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>김하늘</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2019.03.05</v>
+      </c>
+      <c r="C63" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="D63" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E63" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F63" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="G63" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H63" t="str">
+        <v>V2026061759</v>
+      </c>
+      <c r="I63">
+        <v>35000</v>
+      </c>
+      <c r="J63" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K63" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>오지우</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2018.06.30</v>
+      </c>
+      <c r="C64" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="D64" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E64" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F64" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="G64" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H64" t="str">
+        <v>V2026061761</v>
+      </c>
+      <c r="I64">
+        <v>35000</v>
+      </c>
+      <c r="J64" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K64" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>정아라</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2021.01.15</v>
+      </c>
+      <c r="C65" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="D65" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E65" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F65" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="G65" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H65" t="str">
+        <v>V2026061760</v>
+      </c>
+      <c r="I65">
+        <v>35000</v>
+      </c>
+      <c r="J65" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K65" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>강시우</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2020.10.08</v>
+      </c>
+      <c r="C66" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="D66" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E66" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F66" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="G66" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H66" t="str">
+        <v>V2026061762</v>
+      </c>
+      <c r="I66">
+        <v>35000</v>
+      </c>
+      <c r="J66" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K66" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>조하린</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2018.08.14</v>
+      </c>
+      <c r="C67" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="D67" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E67" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F67" t="str">
+        <v>2026.06.17</v>
+      </c>
+      <c r="G67" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H67" t="str">
+        <v>V2026061763</v>
+      </c>
+      <c r="I67">
+        <v>35000</v>
+      </c>
+      <c r="J67" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K67" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>이바다</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2020.07.21</v>
+      </c>
+      <c r="C68" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="D68" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E68" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F68" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="G68" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H68" t="str">
+        <v>V2026061864</v>
+      </c>
+      <c r="I68">
+        <v>35000</v>
+      </c>
+      <c r="J68" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K68" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>한서준</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2020.02.18</v>
+      </c>
+      <c r="C69" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="D69" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E69" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F69" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="G69" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H69" t="str">
+        <v>V2026061865</v>
+      </c>
+      <c r="I69">
+        <v>35000</v>
+      </c>
+      <c r="J69" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K69" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>강시우</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2020.10.08</v>
+      </c>
+      <c r="C70" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="D70" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E70" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F70" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="G70" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H70" t="str">
+        <v>V2026061867</v>
+      </c>
+      <c r="I70">
+        <v>35000</v>
+      </c>
+      <c r="J70" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K70" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>윤서아</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2021.05.11</v>
+      </c>
+      <c r="C71" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="D71" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E71" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F71" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="G71" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H71" t="str">
+        <v>V2026061866</v>
+      </c>
+      <c r="I71">
+        <v>35000</v>
+      </c>
+      <c r="J71" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K71" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>배은우</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2021.04.02</v>
+      </c>
+      <c r="C72" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="D72" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E72" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F72" t="str">
+        <v>2026.06.18</v>
+      </c>
+      <c r="G72" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H72" t="str">
+        <v>V2026061868</v>
+      </c>
+      <c r="I72">
+        <v>35000</v>
+      </c>
+      <c r="J72" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K72" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>박가온</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2018.11.02</v>
+      </c>
+      <c r="C73" t="str">
+        <v>2026.06.19</v>
+      </c>
+      <c r="D73" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E73" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F73" t="str">
+        <v>2026.06.19</v>
+      </c>
+      <c r="G73" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H73" t="str">
+        <v>V2026061969</v>
+      </c>
+      <c r="I73">
+        <v>35000</v>
+      </c>
+      <c r="J73" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K73" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>정아라</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2021.01.15</v>
+      </c>
+      <c r="C74" t="str">
+        <v>2026.06.19</v>
+      </c>
+      <c r="D74" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E74" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F74" t="str">
+        <v>2026.06.19</v>
+      </c>
+      <c r="G74" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H74" t="str">
+        <v>V2026061970</v>
+      </c>
+      <c r="I74">
+        <v>35000</v>
+      </c>
+      <c r="J74" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K74" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>최도윤</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2019.09.09</v>
+      </c>
+      <c r="C75" t="str">
+        <v>2026.06.19</v>
+      </c>
+      <c r="D75" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E75" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F75" t="str">
+        <v>2026.06.19</v>
+      </c>
+      <c r="G75" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H75" t="str">
+        <v>V2026061971</v>
+      </c>
+      <c r="I75">
+        <v>35000</v>
+      </c>
+      <c r="J75" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K75" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>윤서아</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2021.05.11</v>
+      </c>
+      <c r="C76" t="str">
+        <v>2026.06.19</v>
+      </c>
+      <c r="D76" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E76" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F76" t="str">
+        <v>2026.06.19</v>
+      </c>
+      <c r="G76" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H76" t="str">
+        <v>V2026061972</v>
+      </c>
+      <c r="I76">
+        <v>35000</v>
+      </c>
+      <c r="J76" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K76" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>김하늘</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2019.03.05</v>
+      </c>
+      <c r="C77" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="D77" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E77" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F77" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="G77" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H77" t="str">
+        <v>V2026062273</v>
+      </c>
+      <c r="I77">
+        <v>35000</v>
+      </c>
+      <c r="J77" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K77" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>박가온</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2018.11.02</v>
+      </c>
+      <c r="C78" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="D78" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E78" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F78" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="G78" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H78" t="str">
+        <v>V2026062274</v>
+      </c>
+      <c r="I78">
+        <v>35000</v>
+      </c>
+      <c r="J78" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K78" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>한서준</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2020.02.18</v>
+      </c>
+      <c r="C79" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="D79" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E79" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F79" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="G79" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H79" t="str">
+        <v>V2026062275</v>
+      </c>
+      <c r="I79">
+        <v>35000</v>
+      </c>
+      <c r="J79" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K79" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>임도현</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2019.12.25</v>
+      </c>
+      <c r="C80" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="D80" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E80" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F80" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="G80" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H80" t="str">
+        <v>V2026062276</v>
+      </c>
+      <c r="I80">
+        <v>35000</v>
+      </c>
+      <c r="J80" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K80" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>조하린</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2018.08.14</v>
+      </c>
+      <c r="C81" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="D81" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E81" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F81" t="str">
+        <v>2026.06.22</v>
+      </c>
+      <c r="G81" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H81" t="str">
+        <v>V2026062277</v>
+      </c>
+      <c r="I81">
+        <v>35000</v>
+      </c>
+      <c r="J81" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K81" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>이바다</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2020.07.21</v>
+      </c>
+      <c r="C82" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="D82" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E82" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F82" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="G82" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H82" t="str">
+        <v>V2026062378</v>
+      </c>
+      <c r="I82">
+        <v>35000</v>
+      </c>
+      <c r="J82" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K82" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>오지우</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2018.06.30</v>
+      </c>
+      <c r="C83" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="D83" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E83" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F83" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="G83" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H83" t="str">
+        <v>V2026062380</v>
+      </c>
+      <c r="I83">
+        <v>35000</v>
+      </c>
+      <c r="J83" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K83" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>최도윤</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2019.09.09</v>
+      </c>
+      <c r="C84" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="D84" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E84" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F84" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="G84" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H84" t="str">
+        <v>V2026062379</v>
+      </c>
+      <c r="I84">
+        <v>35000</v>
+      </c>
+      <c r="J84" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K84" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>임도현</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2019.12.25</v>
+      </c>
+      <c r="C85" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="D85" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E85" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F85" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="G85" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H85" t="str">
+        <v>V2026062381</v>
+      </c>
+      <c r="I85">
+        <v>35000</v>
+      </c>
+      <c r="J85" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K85" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>배은우</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2021.04.02</v>
+      </c>
+      <c r="C86" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="D86" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E86" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F86" t="str">
+        <v>2026.06.23</v>
+      </c>
+      <c r="G86" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H86" t="str">
+        <v>V2026062382</v>
+      </c>
+      <c r="I86">
+        <v>35000</v>
+      </c>
+      <c r="J86" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K86" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>김하늘</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2019.03.05</v>
+      </c>
+      <c r="C87" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="D87" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E87" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F87" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="G87" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H87" t="str">
+        <v>V2026062483</v>
+      </c>
+      <c r="I87">
+        <v>35000</v>
+      </c>
+      <c r="J87" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K87" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>오지우</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2018.06.30</v>
+      </c>
+      <c r="C88" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="D88" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E88" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F88" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="G88" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H88" t="str">
+        <v>V2026062485</v>
+      </c>
+      <c r="I88">
+        <v>35000</v>
+      </c>
+      <c r="J88" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K88" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>정아라</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2021.01.15</v>
+      </c>
+      <c r="C89" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="D89" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E89" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F89" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="G89" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H89" t="str">
+        <v>V2026062484</v>
+      </c>
+      <c r="I89">
+        <v>35000</v>
+      </c>
+      <c r="J89" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K89" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>강시우</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2020.10.08</v>
+      </c>
+      <c r="C90" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="D90" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E90" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F90" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="G90" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H90" t="str">
+        <v>V2026062486</v>
+      </c>
+      <c r="I90">
+        <v>35000</v>
+      </c>
+      <c r="J90" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K90" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>조하린</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2018.08.14</v>
+      </c>
+      <c r="C91" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="D91" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E91" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F91" t="str">
+        <v>2026.06.24</v>
+      </c>
+      <c r="G91" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H91" t="str">
+        <v>V2026062487</v>
+      </c>
+      <c r="I91">
+        <v>35000</v>
+      </c>
+      <c r="J91" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K91" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>이바다</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2020.07.21</v>
+      </c>
+      <c r="C92" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="D92" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E92" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F92" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="G92" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H92" t="str">
+        <v>V2026062588</v>
+      </c>
+      <c r="I92">
+        <v>35000</v>
+      </c>
+      <c r="J92" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K92" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>한서준</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2020.02.18</v>
+      </c>
+      <c r="C93" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="D93" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E93" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F93" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="G93" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H93" t="str">
+        <v>V2026062589</v>
+      </c>
+      <c r="I93">
+        <v>35000</v>
+      </c>
+      <c r="J93" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K93" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>강시우</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2020.10.08</v>
+      </c>
+      <c r="C94" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="D94" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E94" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F94" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="G94" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H94" t="str">
+        <v>V2026062591</v>
+      </c>
+      <c r="I94">
+        <v>35000</v>
+      </c>
+      <c r="J94" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K94" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>윤서아</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2021.05.11</v>
+      </c>
+      <c r="C95" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="D95" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E95" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F95" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="G95" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H95" t="str">
+        <v>V2026062590</v>
+      </c>
+      <c r="I95">
+        <v>35000</v>
+      </c>
+      <c r="J95" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K95" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>배은우</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2021.04.02</v>
+      </c>
+      <c r="C96" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="D96" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E96" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F96" t="str">
+        <v>2026.06.25</v>
+      </c>
+      <c r="G96" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H96" t="str">
+        <v>V2026062592</v>
+      </c>
+      <c r="I96">
+        <v>35000</v>
+      </c>
+      <c r="J96" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K96" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>박가온</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2018.11.02</v>
+      </c>
+      <c r="C97" t="str">
+        <v>2026.06.26</v>
+      </c>
+      <c r="D97" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E97" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F97" t="str">
+        <v>2026.06.26</v>
+      </c>
+      <c r="G97" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H97" t="str">
+        <v>V2026062693</v>
+      </c>
+      <c r="I97">
+        <v>35000</v>
+      </c>
+      <c r="J97" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K97" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>정아라</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2021.01.15</v>
+      </c>
+      <c r="C98" t="str">
+        <v>2026.06.26</v>
+      </c>
+      <c r="D98" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E98" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F98" t="str">
+        <v>2026.06.26</v>
+      </c>
+      <c r="G98" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H98" t="str">
+        <v>V2026062694</v>
+      </c>
+      <c r="I98">
+        <v>35000</v>
+      </c>
+      <c r="J98" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K98" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>최도윤</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2019.09.09</v>
+      </c>
+      <c r="C99" t="str">
+        <v>2026.06.26</v>
+      </c>
+      <c r="D99" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E99" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F99" t="str">
+        <v>2026.06.26</v>
+      </c>
+      <c r="G99" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H99" t="str">
+        <v>V2026062695</v>
+      </c>
+      <c r="I99">
+        <v>35000</v>
+      </c>
+      <c r="J99" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K99" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>윤서아</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2021.05.11</v>
+      </c>
+      <c r="C100" t="str">
+        <v>2026.06.26</v>
+      </c>
+      <c r="D100" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E100" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F100" t="str">
+        <v>2026.06.26</v>
+      </c>
+      <c r="G100" t="str">
+        <v>12:38</v>
+      </c>
+      <c r="H100" t="str">
+        <v>V2026062696</v>
+      </c>
+      <c r="I100">
+        <v>35000</v>
+      </c>
+      <c r="J100" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K100" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>김하늘</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2019.03.05</v>
+      </c>
+      <c r="C101" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="D101" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E101" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F101" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="G101" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H101" t="str">
+        <v>V2026062997</v>
+      </c>
+      <c r="I101">
+        <v>35000</v>
+      </c>
+      <c r="J101" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K101" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>박가온</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2018.11.02</v>
+      </c>
+      <c r="C102" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="D102" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E102" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F102" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="G102" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H102" t="str">
+        <v>V2026062998</v>
+      </c>
+      <c r="I102">
+        <v>35000</v>
+      </c>
+      <c r="J102" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K102" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>한서준</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2020.02.18</v>
+      </c>
+      <c r="C103" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="D103" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="E103" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="F103" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="G103" t="str">
+        <v>11:32</v>
+      </c>
+      <c r="H103" t="str">
+        <v>V2026062999</v>
+      </c>
+      <c r="I103">
+        <v>35000</v>
+      </c>
+      <c r="J103" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K103" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>임도현</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2019.12.25</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="D104" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E104" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F104" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="G104" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H104" t="str">
+        <v>V20260629100</v>
+      </c>
+      <c r="I104">
+        <v>35000</v>
+      </c>
+      <c r="J104" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K104" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>조하린</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2018.08.14</v>
+      </c>
+      <c r="C105" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="D105" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E105" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F105" t="str">
+        <v>2026.06.29</v>
+      </c>
+      <c r="G105" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H105" t="str">
+        <v>V20260629101</v>
+      </c>
+      <c r="I105">
+        <v>35000</v>
+      </c>
+      <c r="J105" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K105" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>이바다</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2020.07.21</v>
+      </c>
+      <c r="C106" t="str">
         <v>2026.06.30</v>
       </c>
-      <c r="D48" t="str">
-        <v>16:00</v>
-      </c>
-      <c r="E48" t="str">
-        <v>16:50</v>
-      </c>
-      <c r="F48" t="str">
+      <c r="D106" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="E106" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="F106" t="str">
         <v>2026.06.30</v>
       </c>
-      <c r="G48" t="str">
-        <v>16:52</v>
-      </c>
-      <c r="H48" t="str">
-        <v>V2026063044</v>
-      </c>
-      <c r="I48">
-        <v>35000</v>
-      </c>
-      <c r="J48" t="str">
-        <v>햇살아동발달센터</v>
-      </c>
-      <c r="K48" t="str">
+      <c r="G106" t="str">
+        <v>09:52</v>
+      </c>
+      <c r="H106" t="str">
+        <v>V20260630102</v>
+      </c>
+      <c r="I106">
+        <v>35000</v>
+      </c>
+      <c r="J106" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K106" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>오지우</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2018.06.30</v>
+      </c>
+      <c r="C107" t="str">
+        <v>2026.06.30</v>
+      </c>
+      <c r="D107" t="str">
+        <v>09:50</v>
+      </c>
+      <c r="E107" t="str">
+        <v>10:40</v>
+      </c>
+      <c r="F107" t="str">
+        <v>2026.06.30</v>
+      </c>
+      <c r="G107" t="str">
+        <v>10:42</v>
+      </c>
+      <c r="H107" t="str">
+        <v>V20260630104</v>
+      </c>
+      <c r="I107">
+        <v>35000</v>
+      </c>
+      <c r="J107" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K107" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>최도윤</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2019.09.09</v>
+      </c>
+      <c r="C108" t="str">
+        <v>2026.06.30</v>
+      </c>
+      <c r="D108" t="str">
+        <v>11:30</v>
+      </c>
+      <c r="E108" t="str">
+        <v>12:20</v>
+      </c>
+      <c r="F108" t="str">
+        <v>2026.06.30</v>
+      </c>
+      <c r="G108" t="str">
+        <v>12:22</v>
+      </c>
+      <c r="H108" t="str">
+        <v>V20260630103</v>
+      </c>
+      <c r="I108">
+        <v>35000</v>
+      </c>
+      <c r="J108" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K108" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>임도현</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2019.12.25</v>
+      </c>
+      <c r="C109" t="str">
+        <v>2026.06.30</v>
+      </c>
+      <c r="D109" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="E109" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="F109" t="str">
+        <v>2026.06.30</v>
+      </c>
+      <c r="G109" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="H109" t="str">
+        <v>V20260630105</v>
+      </c>
+      <c r="I109">
+        <v>35000</v>
+      </c>
+      <c r="J109" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K109" t="str">
+        <v>정상결제</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>배은우</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2021.04.02</v>
+      </c>
+      <c r="C110" t="str">
+        <v>2026.06.30</v>
+      </c>
+      <c r="D110" t="str">
+        <v>14:20</v>
+      </c>
+      <c r="E110" t="str">
+        <v>15:10</v>
+      </c>
+      <c r="F110" t="str">
+        <v>2026.06.30</v>
+      </c>
+      <c r="G110" t="str">
+        <v>15:12</v>
+      </c>
+      <c r="H110" t="str">
+        <v>V20260630106</v>
+      </c>
+      <c r="I110">
+        <v>35000</v>
+      </c>
+      <c r="J110" t="str">
+        <v>햇살아동발달센터</v>
+      </c>
+      <c r="K110" t="str">
         <v>정상결제</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K110"/>
   </ignoredErrors>
 </worksheet>
 </file>